--- a/out/Attention-mamba2_repeat_2_000008.xlsx
+++ b/out/Attention-mamba2_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.60677127013091</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.60677127013091</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-3.60677127013091</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-3.60677127013091</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC45" t="n">
-        <v>-1.77310559846228e-05</v>
+        <v>-0.0001580500369600486</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.02037004320095765</v>
+        <v>-0.1815691361593498</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.60677127013091</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.1817271861963099</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-3.60677127013091</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.02039660986558022</v>
+        <v>-0.1818491598514079</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.03177083643561986</v>
+        <v>0.4385892286320073</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-3.60677127013091</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.04320606417502405</v>
+        <v>0.696171919271053</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002260672877664197</v>
+        <v>0.03124942704189036</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-3.60677127013091</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.0159086021337742</v>
+        <v>0.3193774851432363</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.003966554242390887</v>
+        <v>0.0548007193722138</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.02158043339071772</v>
+        <v>0.3977193251257315</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.004819494924754243</v>
+        <v>0.06657640212364128</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.0272525668227484</v>
+        <v>0.4760665631682023</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.001271760340953602</v>
+        <v>0.01761778408680689</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.02497166671671707</v>
+        <v>0.4446404347924448</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0007041646792803888</v>
+        <v>0.009787562658743995</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-3.00677127013091</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.0251075894669391</v>
+        <v>0.4465808715012805</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.001485546532498157</v>
+        <v>0.0205649487540083</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.02737492341447889</v>
+        <v>0.4779356184364124</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0005799485605439023</v>
+        <v>0.00807649429505064</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02704931563952134</v>
+        <v>0.473505755748797</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.0004124343027119488</v>
+        <v>0.00574938361093827</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.02729278037683142</v>
+        <v>0.4769263874329142</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.000159304835060317</v>
+        <v>0.002259962519674452</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.02719863086378865</v>
+        <v>0.4756920828591106</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>8.748479002056815e-05</v>
+        <v>0.001280538581285897</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.02721574229196832</v>
+        <v>0.4759920614330843</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.023107692045166e-05</v>
+        <v>0.000484711969194278</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.02718827823672665</v>
+        <v>0.4756795516206713</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>1.151440665124258e-05</v>
+        <v>0.00022510073267398</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.02718097741556458</v>
+        <v>0.4756435175704514</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>1.458602354831796e-06</v>
+        <v>7.896183061281334e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.02717126447640522</v>
+        <v>0.4755769553734451</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.092056993363991e-06</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.0271636156064258</v>
+        <v>0.4755371893272863</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>-4.046028496681996e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.02715861411714181</v>
+        <v>0.4755321699665931</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-4.486309854708224e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.4755281519222495</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.02715387056784437</v>
+        <v>0.4755257172520587</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.4755202000100689</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.02715346633443422</v>
+        <v>0.475513876016061</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.02715328259197518</v>
+        <v>0.4755085082274827</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.02715331934046699</v>
+        <v>0.4755085449759744</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.02715342958594242</v>
+        <v>0.4755086552214499</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.02715350308292604</v>
+        <v>0.4755087287184335</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.4755089124608927</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.02715523026204179</v>
+        <v>0.4755104558975491</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.02715670020171464</v>
+        <v>0.4755119258372222</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.02715794965043664</v>
+        <v>0.4755131752859442</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.02715930934463406</v>
+        <v>0.4755145349801416</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.02715710443512478</v>
+        <v>0.4755123300706323</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.02715670020171464</v>
+        <v>0.4755119258372222</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.4755110806219103</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2927231521932764</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.02715640621378005</v>
+        <v>0.4755116318492875</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.02715607547735365</v>
+        <v>0.4755113011128612</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02715578148941905</v>
+        <v>0.4755110071249267</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.4755110806219103</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02715541400450084</v>
+        <v>0.4755106396400083</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02715530375902541</v>
+        <v>0.4755105293945328</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.0271552670105336</v>
+        <v>0.4755104926460411</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02715541400450084</v>
+        <v>0.4755106396400083</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.0271549362741072</v>
+        <v>0.4755101619096147</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.0271558917348946</v>
+        <v>0.475511117370402</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.4755110806219103</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02715552424997638</v>
+        <v>0.4755107498854839</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2927231521932764</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02715596523187822</v>
+        <v>0.4755111908673858</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02715534050751722</v>
+        <v>0.4755105661430247</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02715515676505817</v>
+        <v>0.4755103824005655</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02715475253164803</v>
+        <v>0.4755099781671555</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.02715390731633617</v>
+        <v>0.4755091329518435</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.02715387056784437</v>
+        <v>0.4755090962033519</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0271540175618116</v>
+        <v>0.4755092431973191</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.02715394406482799</v>
+        <v>0.4755091697003355</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0271540175618116</v>
+        <v>0.4755092431973191</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.02715405431030342</v>
+        <v>0.475509279945811</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.02715394406482799</v>
+        <v>0.4755091697003355</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.02715438504672982</v>
+        <v>0.4755096106822374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.02715427480125439</v>
+        <v>0.4755095004367619</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.02715423805276258</v>
+        <v>0.47550946368827</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.02715416455577884</v>
+        <v>0.4755093901912864</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.02715412780728703</v>
+        <v>0.4755093534427947</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.02715390731633617</v>
+        <v>0.4755091329518435</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.02715383381935244</v>
+        <v>0.4755090594548599</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.02715376032236882</v>
+        <v>0.4755089859578763</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.4755090227063682</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.4755089124608927</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.4755090227063682</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.02715409105879522</v>
+        <v>0.4755093166943027</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000008.xlsx
+++ b/out/Attention-mamba2_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2927231521932764</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8927231521932764</v>
+        <v>-0.3248742778844245</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-3.60677127013091</v>
+        <v>-0.3248742778844246</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844245</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-3.60677127013091</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8927231521932764</v>
+        <v>-0.3248742778844246</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC45" t="n">
-        <v>-1.77310559846228e-05</v>
+        <v>-4.736684697121382e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.02037004320095765</v>
+        <v>-0.05441540952835031</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.02038777425694221</v>
+        <v>-0.05446277637532144</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.02039660986558022</v>
+        <v>-0.05452355245892424</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.03177083643561986</v>
+        <v>0.2185369554531779</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.04320606417502405</v>
+        <v>0.382969957404451</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002260672877664197</v>
+        <v>0.0155706756066454</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-3.60677127013091</v>
+        <v>-2.307500299518339</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.0159086021337742</v>
+        <v>0.1952238692358337</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.003966554242390887</v>
+        <v>0.02730565975612756</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-3.60677127013091</v>
+        <v>-1.416187288701382</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.02158043339071772</v>
+        <v>0.2342595005878834</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.004819494924754243</v>
+        <v>0.03317346361740247</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.0272525668227484</v>
+        <v>0.2732979132547553</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.001271760340953602</v>
+        <v>0.008777143343425095</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8927231521932764</v>
+        <v>-0.5248742778844246</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.02497166671671707</v>
+        <v>0.2576379342602715</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0007041646792803888</v>
+        <v>0.004874405191117006</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-3.00677127013091</v>
+        <v>-0.3248742778844246</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.0251075894669391</v>
+        <v>0.2586022999214253</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.001485546532498157</v>
+        <v>0.01024539756061297</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8927231521932764</v>
+        <v>-0.3248742778844246</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.02737492341447889</v>
+        <v>0.2742240018357376</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0005799485605439023</v>
+        <v>0.004021819800845703</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02704931563952134</v>
+        <v>0.2720141961357044</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.0004124343027119488</v>
+        <v>0.002861842194658095</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.02729278037683142</v>
+        <v>0.2737161089344625</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.000159304835060317</v>
+        <v>0.001123407586240689</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.02719863086378865</v>
+        <v>0.2730984832236066</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>8.748479002056815e-05</v>
+        <v>0.0006362278774759392</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.02721574229196832</v>
+        <v>0.2732455151779354</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.023107692045166e-05</v>
+        <v>0.0002392687999817981</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.02718827823672665</v>
+        <v>0.2730873122903598</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>1.151440665124258e-05</v>
+        <v>0.0001094998861152819</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.02718097741556458</v>
+        <v>0.2730668695093891</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>1.458602354831796e-06</v>
+        <v>3.698091530640667e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.02717126447640522</v>
+        <v>0.2730312354048535</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.092056993363991e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.0271636156064258</v>
+        <v>0.2730090177499873</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>-4.046028496681996e-06</v>
+        <v>1.200814771567029e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.5664387329325324</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.02715861411714181</v>
+        <v>0.273004008069641</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-4.486309854708224e-06</v>
+        <v>-1.917859128249343e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.2729994810675932</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-2.908363659633048e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.02715387056784437</v>
+        <v>0.2729957642371135</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.2729904684071094</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.02715346633443422</v>
+        <v>0.2729848064101056</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.02715328259197518</v>
+        <v>0.2729846226676465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.02715331934046699</v>
+        <v>0.2729846594161382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.02715342958594242</v>
+        <v>0.2729847696616137</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.02715350308292604</v>
+        <v>0.2729848431585973</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.2729850269010565</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.02715523026204179</v>
+        <v>0.272986570337713</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.02715670020171464</v>
+        <v>0.2729880402773861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.02715794965043664</v>
+        <v>0.2729892897261081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.02715930934463406</v>
+        <v>0.2729906494203054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.02715710443512478</v>
+        <v>0.2729884445107961</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.02715670020171464</v>
+        <v>0.2729880402773861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.2729871950620741</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.02715640621378005</v>
+        <v>0.2729877462894514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.02715607547735365</v>
+        <v>0.272987415553025</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02715578148941905</v>
+        <v>0.2729871215650905</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.2729871950620741</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02715541400450084</v>
+        <v>0.2729867540801721</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02715530375902541</v>
+        <v>0.2729866438346966</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.0271552670105336</v>
+        <v>0.2729866070862049</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02715541400450084</v>
+        <v>0.2729867540801721</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.0271549362741072</v>
+        <v>0.2729862763497785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.0271558917348946</v>
+        <v>0.2729872318105658</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02715585498640279</v>
+        <v>0.2729871950620741</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02715552424997638</v>
+        <v>0.2729868643256477</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02715596523187822</v>
+        <v>0.2729873053075497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02715534050751722</v>
+        <v>0.2729866805831885</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02715515676505817</v>
+        <v>0.2729864968407294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02715475253164803</v>
+        <v>0.2729860926073194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.02715390731633617</v>
+        <v>0.2729852473920074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.02715387056784437</v>
+        <v>0.2729852106435157</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0271540175618116</v>
+        <v>0.2729853576374829</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.02715394406482799</v>
+        <v>0.2729852841404993</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0271540175618116</v>
+        <v>0.2729853576374829</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.02715405431030342</v>
+        <v>0.2729853943859749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.02715394406482799</v>
+        <v>0.2729852841404993</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.02715438504672982</v>
+        <v>0.2729857251224013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.02715427480125439</v>
+        <v>0.2729856148769257</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.02715423805276258</v>
+        <v>0.2729855781284338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.02715416455577884</v>
+        <v>0.2729855046314502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.02715412780728703</v>
+        <v>0.2729854678829585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.02715390731633617</v>
+        <v>0.2729852473920074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.02715383381935244</v>
+        <v>0.2729851738950237</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.02715376032236882</v>
+        <v>0.2729851003980401</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.2729851371465321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.0271536868253852</v>
+        <v>0.2729850269010565</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.02715379707086063</v>
+        <v>0.2729851371465321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2927231521932764</v>
+        <v>0.3664387329325325</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.02715409105879522</v>
+        <v>0.2729854311344665</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000008.xlsx
+++ b/out/Attention-mamba2_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2624114155769348</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3613953292369843</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.2942568063735962</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.007352031767368317</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.09022143483161926</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03019993007183075</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0001189038157463074</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.02973118424415588</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02356372773647308</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.02977742254734039</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.02743002772331238</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.03111693263053894</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.03548610210418701</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.03658223897218704</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3248742778844245</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01526393741369247</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3248742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01750477403402328</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5248742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.04320491850376129</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.03954272717237473</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.03996402025222778</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.04540093988180161</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.04654447734355927</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.04668154567480087</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.04821533709764481</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.04189790785312653</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0423518568277359</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.04801705479621887</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.04729003459215164</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.04857842624187469</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.04806508868932724</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.03367834538221359</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5248742778844245</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.05558079108595848</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007678613066673279</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02762644737958908</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.03087453544139862</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.03663071990013123</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02949002385139465</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.04376721382141113</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.04878212511539459</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01009445637464523</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3248742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.003736197948455811</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001065168529748917</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1295737326145172</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0830514058470726</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.1151521950960159</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-4.736684697121382e-05</v>
+        <v>-8.357703990372829e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05441540952835031</v>
+        <v>-0.09601396639919664</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1441503465175629</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02897898107767105</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5248742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.1554025709629059</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.1069411784410477</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.1245725154876709</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.1045026779174805</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.1119842827320099</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.1022228896617889</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.1370580941438675</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.1312384456396103</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.1592104583978653</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.1572766900062561</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.06411705911159515</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.05446277637532144</v>
+        <v>-0.0960975434391005</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.1194862201809883</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.05452355245892424</v>
+        <v>-0.09617470921114693</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2185369554531779</v>
+        <v>0.2774705424992745</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0174465999007225</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.382969957404451</v>
+        <v>0.4592991293896239</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0155706756066454</v>
+        <v>0.01976968131022419</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.04562438279390335</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.307500299518339</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1952238692358337</v>
+        <v>0.2209229296398077</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02730565975612756</v>
+        <v>0.03466941338999476</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.04395012557506561</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.416187288701382</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2342595005878834</v>
+        <v>0.270485404310894</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03317346361740247</v>
+        <v>0.04211924284361454</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.03169265389442444</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2732979132547553</v>
+        <v>0.3200511777950546</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.008777143343425095</v>
+        <v>0.01114543967796355</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.09375032782554626</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5248742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2576379342602715</v>
+        <v>0.3001695718389565</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004874405191117006</v>
+        <v>0.006190010229864794</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01743070781230927</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3248742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2586022999214253</v>
+        <v>0.301395338553933</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01024539756061297</v>
+        <v>0.01300915136906095</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001913070678710938</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3248742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2742240018357376</v>
+        <v>0.32123155123688</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004021819800845703</v>
+        <v>0.005108152841855809</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.05774813890457153</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2720141961357044</v>
+        <v>0.3184269453224319</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002861842194658095</v>
+        <v>0.003636338070350925</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.1084622144699097</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2737161089344625</v>
+        <v>0.3205893381342557</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001123407586240689</v>
+        <v>0.001427575214782102</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.1053772270679474</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2730984832236066</v>
+        <v>0.3198066753083458</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006362278774759392</v>
+        <v>0.0008088661521809998</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.1142110824584961</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2732455151779354</v>
+        <v>0.3199946389426859</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002392687999817981</v>
+        <v>0.0003050334768999746</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.1125419586896896</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2730873122903598</v>
+        <v>0.3197951891238403</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001094998861152819</v>
+        <v>0.0001403267785309347</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.1010467857122421</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2730668695093891</v>
+        <v>0.3197705886710698</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.698091530640667e-05</v>
+        <v>4.828346942736231e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1088158190250397</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2730312354048535</v>
+        <v>0.3197267069230051</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.1063112318515778</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5664387329325324</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2730090177499873</v>
+        <v>0.3196998537456749</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.200814771567029e-06</v>
+        <v>2.631772026544036e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.1007568091154099</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5664387329325324</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.273004008069641</v>
+        <v>0.3196948418314022</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.1103431582450867</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2729994810675932</v>
+        <v>0.3196904602458414</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.07588577270507812</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2729957642371135</v>
+        <v>0.3196871098910486</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1019767820835114</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2729904684071094</v>
+        <v>0.3196817405640608</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.08284083008766174</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2729848064101056</v>
+        <v>0.3196757478306305</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.07532121241092682</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2729846226676465</v>
+        <v>0.3196703800420521</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02454274147748947</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2729846594161382</v>
+        <v>0.3196704167905438</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.09096257388591766</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2729847696616137</v>
+        <v>0.3196705270360194</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.08402138948440552</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2729848431585973</v>
+        <v>0.319670600533003</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.1144930422306061</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2729850269010565</v>
+        <v>0.3196707842754621</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.08546406030654907</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.272986570337713</v>
+        <v>0.3196723277121186</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.08526028692722321</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2729880402773861</v>
+        <v>0.3196737976517917</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.06392614543437958</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2729892897261081</v>
+        <v>0.3196750471005137</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01169584691524506</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2729906494203054</v>
+        <v>0.319676406794711</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.05186250805854797</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2729884445107961</v>
+        <v>0.3196742018852017</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.042064368724823</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2729880402773861</v>
+        <v>0.3196737976517917</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03597430139780045</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2729871950620741</v>
+        <v>0.3196729524364798</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.08976921439170837</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2729877462894514</v>
+        <v>0.319673503663857</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.09796197712421417</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.272987415553025</v>
+        <v>0.3196731729274306</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.1038305312395096</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2729871215650905</v>
+        <v>0.3196728789394961</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.1059987843036652</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2729871950620741</v>
+        <v>0.3196729524364798</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.1014421880245209</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2729867540801721</v>
+        <v>0.3196725114545778</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.09995634853839874</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2729866438346966</v>
+        <v>0.3196724012091022</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.1046980023384094</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2729866070862049</v>
+        <v>0.3196723644606105</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.1136683821678162</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2729867540801721</v>
+        <v>0.3196725114545778</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.06356380879878998</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2729862763497785</v>
+        <v>0.3196720337241841</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.03488624840974808</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2729872318105658</v>
+        <v>0.3196729891849714</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.09661649167537689</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2729871950620741</v>
+        <v>0.3196729524364798</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.1070778965950012</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2729868643256477</v>
+        <v>0.3196726217000533</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.1017895638942719</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2729873053075497</v>
+        <v>0.3196730626819553</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.1087155938148499</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2729866805831885</v>
+        <v>0.3196724379575941</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.1113046407699585</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2729864968407294</v>
+        <v>0.319672254215135</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.1024873107671738</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2729860926073194</v>
+        <v>0.319671849981725</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.09857344627380371</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2729852473920074</v>
+        <v>0.319671004766413</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.1120649129152298</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2729852106435157</v>
+        <v>0.3196709680179213</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.1038471460342407</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2729853576374829</v>
+        <v>0.3196711150118886</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.116256058216095</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2729852841404993</v>
+        <v>0.3196710415149049</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.04092110693454742</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2729853576374829</v>
+        <v>0.3196711150118886</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.1074507534503937</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2729853943859749</v>
+        <v>0.3196711517603805</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.09279218316078186</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2729852841404993</v>
+        <v>0.3196710415149049</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.1126682460308075</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2729857251224013</v>
+        <v>0.3196714824968069</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.1106126308441162</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2729856148769257</v>
+        <v>0.3196713722513314</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0851881206035614</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2729855781284338</v>
+        <v>0.3196713355028394</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.09862753748893738</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2729855046314502</v>
+        <v>0.3196712620058558</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.09352564811706543</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2729854678829585</v>
+        <v>0.3196712252573641</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.07138806581497192</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2729852473920074</v>
+        <v>0.319671004766413</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.1045906245708466</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2729851738950237</v>
+        <v>0.3196709312694294</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.08702902495861053</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2729851003980401</v>
+        <v>0.3196708577724457</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.08671098947525024</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2729851371465321</v>
+        <v>0.3196708945209377</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.1035648286342621</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2729850269010565</v>
+        <v>0.3196707842754621</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.08229988813400269</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3664387329325325</v>
+        <v>-0.4399999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2729851371465321</v>
+        <v>0.3196708945209377</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0935935378074646</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3664387329325325</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2729854311344665</v>
+        <v>0.3196711885088722</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000008.xlsx
+++ b/out/Attention-mamba2_repeat_2_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.2624114155769348</v>
+        <v>-0.2624304294586182</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3613953292369843</v>
+        <v>-0.3614038825035095</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.2942568063735962</v>
+        <v>-0.2943130731582642</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.007352031767368317</v>
+        <v>0.0073099285364151</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.09022143483161926</v>
+        <v>-0.09024430811405182</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.03019993007183075</v>
+        <v>-0.03025688603520393</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0001189038157463074</v>
+        <v>-0.0002017617225646973</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.02973118424415588</v>
+        <v>0.02964063733816147</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.02356372773647308</v>
+        <v>0.02347221970558167</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.02977742254734039</v>
+        <v>0.02968548983335495</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.02743002772331238</v>
+        <v>0.02733704447746277</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.03111693263053894</v>
+        <v>0.03102243691682816</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.03548610210418701</v>
+        <v>0.03539028763771057</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.03658223897218704</v>
+        <v>0.03648839145898819</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.01526393741369247</v>
+        <v>-0.01534392684698105</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.01750477403402328</v>
+        <v>0.01741844415664673</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.04320491850376129</v>
+        <v>0.04310953617095947</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.03954272717237473</v>
+        <v>0.03944458812475204</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.03996402025222778</v>
+        <v>0.03986556082963943</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.04540093988180161</v>
+        <v>0.04530201107263565</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.04654447734355927</v>
+        <v>0.0464448481798172</v>
       </c>
       <c r="JB22" t="n">
         <v>0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.04668154567480087</v>
+        <v>0.04658212512731552</v>
       </c>
       <c r="JB23" t="n">
         <v>0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.04821533709764481</v>
+        <v>0.04811640828847885</v>
       </c>
       <c r="JB24" t="n">
         <v>0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.04189790785312653</v>
+        <v>0.04179990291595459</v>
       </c>
       <c r="JB25" t="n">
         <v>0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0423518568277359</v>
+        <v>0.04225417971611023</v>
       </c>
       <c r="JB26" t="n">
         <v>0.2599999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.04801705479621887</v>
+        <v>0.04791870713233948</v>
       </c>
       <c r="JB27" t="n">
         <v>0.2599999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.04729003459215164</v>
+        <v>0.04719069600105286</v>
       </c>
       <c r="JB28" t="n">
         <v>0.2599999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.04857842624187469</v>
+        <v>0.04847897589206696</v>
       </c>
       <c r="JB29" t="n">
         <v>0.2599999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.04806508868932724</v>
+        <v>0.04796644300222397</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.02000000000000007</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.03367834538221359</v>
+        <v>0.03358767926692963</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.05558079108595848</v>
+        <v>-0.05564027652144432</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.007678613066673279</v>
+        <v>0.007609255611896515</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.02762644737958908</v>
+        <v>0.02754053473472595</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.03087453544139862</v>
+        <v>0.03078258037567139</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.03663071990013123</v>
+        <v>0.03653787821531296</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.02949002385139465</v>
+        <v>0.02939588576555252</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.04376721382141113</v>
+        <v>0.04366984963417053</v>
       </c>
       <c r="JB38" t="n">
         <v>0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.04878212511539459</v>
+        <v>0.04868628084659576</v>
       </c>
       <c r="JB39" t="n">
         <v>0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01009445637464523</v>
+        <v>0.01000803709030151</v>
       </c>
       <c r="JB40" t="n">
         <v>0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.003736197948455811</v>
+        <v>-0.003814809024333954</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001065168529748917</v>
+        <v>-0.001143887639045715</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.1295737326145172</v>
+        <v>-0.1296390295028687</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0830514058470726</v>
+        <v>-0.08310885727405548</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.1151521950960159</v>
+        <v>-0.1151145622134209</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1441503465175629</v>
+        <v>-0.144141361117363</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02897898107767105</v>
+        <v>0.02893310040235519</v>
       </c>
       <c r="JB47" t="n">
         <v>0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.1554025709629059</v>
+        <v>0.1553278714418411</v>
       </c>
       <c r="JB48" t="n">
         <v>0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.1069411784410477</v>
+        <v>0.106897383928299</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.1245725154876709</v>
+        <v>0.1245346218347549</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.1045026779174805</v>
+        <v>0.1044755578041077</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1119842827320099</v>
+        <v>0.1119567006826401</v>
       </c>
       <c r="JB52" t="n">
         <v>0.8599999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.1022228896617889</v>
+        <v>0.1022068113088608</v>
       </c>
       <c r="JB53" t="n">
         <v>0.8599999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.1370580941438675</v>
+        <v>0.1370339244604111</v>
       </c>
       <c r="JB54" t="n">
         <v>0.8599999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.1312384456396103</v>
+        <v>0.1312246471643448</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.1592104583978653</v>
+        <v>0.1591900885105133</v>
       </c>
       <c r="JB56" t="n">
         <v>0.8599999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1572766900062561</v>
+        <v>0.1572668552398682</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.02000000000000007</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.06411705911159515</v>
+        <v>0.06412452459335327</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.1194862201809883</v>
+        <v>-0.1194381043314934</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0174465999007225</v>
+        <v>-0.01730120927095413</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.8599999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.04562438279390335</v>
+        <v>-0.0454089492559433</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.8599999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.04395012557506561</v>
+        <v>-0.04374312609434128</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.5799999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.03169265389442444</v>
+        <v>0.03179419785737991</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.09375032782554626</v>
+        <v>0.09367494285106659</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.5799999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.01743070781230927</v>
+        <v>-0.01720737665891647</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.001913070678710938</v>
+        <v>0.002247564494609833</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.05774813890457153</v>
+        <v>0.05787083506584167</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.1084622144699097</v>
+        <v>0.1084302067756653</v>
       </c>
       <c r="JB68" t="n">
         <v>0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1053772270679474</v>
+        <v>0.1053631007671356</v>
       </c>
       <c r="JB69" t="n">
         <v>0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.1142110824584961</v>
+        <v>0.1141735017299652</v>
       </c>
       <c r="JB70" t="n">
         <v>0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1125419586896896</v>
+        <v>0.1124992519617081</v>
       </c>
       <c r="JB71" t="n">
         <v>0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1010467857122421</v>
+        <v>0.1010047793388367</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1088158190250397</v>
+        <v>0.108780711889267</v>
       </c>
       <c r="JB73" t="n">
         <v>0.8599999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.1063112318515778</v>
+        <v>0.1062750071287155</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1007568091154099</v>
+        <v>0.1007196009159088</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.02000000000000007</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1103431582450867</v>
+        <v>0.1102965474128723</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.07588577270507812</v>
+        <v>0.07584628462791443</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.3</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1019767820835114</v>
+        <v>0.101935938000679</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.08284083008766174</v>
+        <v>0.08281324803829193</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.07532121241092682</v>
+        <v>0.07530134916305542</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.02454274147748947</v>
+        <v>0.02465724945068359</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.09096257388591766</v>
+        <v>0.09092622995376587</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.08402138948440552</v>
+        <v>0.08398288488388062</v>
       </c>
       <c r="JB83" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.1144930422306061</v>
+        <v>0.1144496500492096</v>
       </c>
       <c r="JB84" t="n">
         <v>0.8599999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.08546406030654907</v>
+        <v>0.08548411726951599</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.08526028692722321</v>
+        <v>0.08521364629268646</v>
       </c>
       <c r="JB86" t="n">
         <v>0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.06392614543437958</v>
+        <v>0.06387197971343994</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.01169584691524506</v>
+        <v>0.0119161531329155</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.05186250805854797</v>
+        <v>0.05234608054161072</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.042064368724823</v>
+        <v>0.04257836937904358</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.03597430139780045</v>
+        <v>0.03648029267787933</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.08976921439170837</v>
+        <v>0.08979490399360657</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.16</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.09796197712421417</v>
+        <v>0.09794223308563232</v>
       </c>
       <c r="JB93" t="n">
         <v>0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.1038305312395096</v>
+        <v>0.1038115173578262</v>
       </c>
       <c r="JB94" t="n">
         <v>0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.1059987843036652</v>
+        <v>0.1059784591197968</v>
       </c>
       <c r="JB95" t="n">
         <v>0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.1014421880245209</v>
+        <v>0.101403996348381</v>
       </c>
       <c r="JB96" t="n">
         <v>0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.09995634853839874</v>
+        <v>0.09991911053657532</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.1046980023384094</v>
+        <v>0.1046613752841949</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1136683821678162</v>
+        <v>0.1136270761489868</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.06356380879878998</v>
+        <v>0.06395566463470459</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.03488624840974808</v>
+        <v>0.0353676825761795</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.09661649167537689</v>
+        <v>0.09662623703479767</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.1070778965950012</v>
+        <v>0.1070502698421478</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.16</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1017895638942719</v>
+        <v>0.1017583906650543</v>
       </c>
       <c r="JB104" t="n">
         <v>0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1087155938148499</v>
+        <v>0.1086857914924622</v>
       </c>
       <c r="JB105" t="n">
         <v>0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1113046407699585</v>
+        <v>0.111272931098938</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1024873107671738</v>
+        <v>0.1024920791387558</v>
       </c>
       <c r="JB107" t="n">
         <v>0.8599999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.09857344627380371</v>
+        <v>0.09857004880905151</v>
       </c>
       <c r="JB108" t="n">
         <v>0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.1120649129152298</v>
+        <v>0.1120264679193497</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.1038471460342407</v>
+        <v>0.1038266718387604</v>
       </c>
       <c r="JB110" t="n">
         <v>0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.116256058216095</v>
+        <v>0.1162010431289673</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.02000000000000007</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.04092110693454742</v>
+        <v>0.04119770228862762</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.1600000000000001</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.1074507534503937</v>
+        <v>0.1074041426181793</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.02000000000000007</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.09279218316078186</v>
+        <v>0.09279409050941467</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.16</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.1126682460308075</v>
+        <v>0.1126226782798767</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.02000000000000007</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.1106126308441162</v>
+        <v>0.110564261674881</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0851881206035614</v>
+        <v>0.0851476788520813</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.09862753748893738</v>
+        <v>0.09858345985412598</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.09352564811706543</v>
+        <v>0.09348011016845703</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.07138806581497192</v>
+        <v>0.07135248184204102</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.5799999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.1045906245708466</v>
+        <v>0.1045463979244232</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.08702902495861053</v>
+        <v>0.0869888961315155</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.08671098947525024</v>
+        <v>0.08667249977588654</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.1035648286342621</v>
+        <v>0.1035246104001999</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.08229988813400269</v>
+        <v>0.08235117793083191</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.4399999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0935935378074646</v>
+        <v>0.09358508884906769</v>
       </c>
       <c r="JB126" t="n">
         <v>0.3000000000000002</v>
